--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H541" s="2" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H597" s="2" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H618" s="2" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H619" s="2" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H620" s="2" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G621" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H621" s="2" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H624" s="2" t="inlineStr">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="G625" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H625" s="2" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H646" s="2" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="G647" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H647" s="2" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H648" s="2" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="G649" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H649" s="2" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="G652" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H652" s="2" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H541" s="2" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H597" s="2" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H618" s="2" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H619" s="2" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H620" s="2" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G621" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H621" s="2" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H624" s="2" t="inlineStr">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="G625" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H625" s="2" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H646" s="2" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="G647" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H647" s="2" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H648" s="2" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="G649" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H649" s="2" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="G652" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H652" s="2" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H541" s="2" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H597" s="2" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H618" s="2" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H619" s="2" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H620" s="2" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G621" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H621" s="2" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H624" s="2" t="inlineStr">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="G625" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H625" s="2" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H646" s="2" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="G647" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H647" s="2" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H648" s="2" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="G649" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H649" s="2" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="G652" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H652" s="2" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H541" s="2" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H597" s="2" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H618" s="2" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H619" s="2" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H620" s="2" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G621" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H621" s="2" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H624" s="2" t="inlineStr">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="G625" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H625" s="2" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H646" s="2" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="G647" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H647" s="2" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H648" s="2" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="G649" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H649" s="2" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="G652" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H652" s="2" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H541" s="2" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H597" s="2" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H618" s="2" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H619" s="2" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H620" s="2" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G621" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H621" s="2" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H624" s="2" t="inlineStr">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="G625" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H625" s="2" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H646" s="2" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="G647" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H647" s="2" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H648" s="2" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="G649" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H649" s="2" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="G652" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H652" s="2" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H541" s="2" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
@@ -27120,7 +27120,7 @@
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H597" s="2" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H618" s="2" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H619" s="2" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H620" s="2" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G621" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H621" s="2" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H624" s="2" t="inlineStr">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="G625" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H625" s="2" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H646" s="2" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="G647" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H647" s="2" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H648" s="2" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="G649" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H649" s="2" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="G652" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H652" s="2" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="G653" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H653" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -589,49 +589,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -803,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +850,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>550</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +961,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
     </row>
@@ -1303,22 +1299,22 @@
         <v>56</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1377,22 @@
         <v>56</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -1459,22 +1455,22 @@
         <v>56</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.7%</t>
         </is>
       </c>
     </row>
@@ -1537,22 +1533,22 @@
         <v>56</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -1615,22 +1611,22 @@
         <v>56</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
@@ -1693,22 +1689,22 @@
         <v>56</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -1771,22 +1767,22 @@
         <v>56</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
     </row>
@@ -1849,22 +1845,22 @@
         <v>56</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>85.6%</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1923,22 @@
         <v>56</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2005,22 +2001,22 @@
         <v>56</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2079,22 @@
         <v>56</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -2161,22 +2157,22 @@
         <v>56</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -2373,49 +2369,45 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -3642,49 +3634,45 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>18/31</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4866,49 +4854,45 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>18/31</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6090,49 +6074,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>6/19</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7318,49 +7298,45 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>6/19</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8546,49 +8522,45 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>16/21</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9770,49 +9742,45 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H199" s="4" t="inlineStr">
-        <is>
-          <t>16/21</t>
-        </is>
-      </c>
-      <c r="I199" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10994,49 +10962,45 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B227" s="4" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C227" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E227" s="4" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F227" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G227" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H227" s="4" t="inlineStr">
-        <is>
-          <t>30/31</t>
-        </is>
-      </c>
-      <c r="I227" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12218,49 +12182,45 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B255" s="4" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C255" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D255" s="4" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E255" s="4" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F255" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G255" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H255" s="4" t="inlineStr">
-        <is>
-          <t>30/31</t>
-        </is>
-      </c>
-      <c r="I255" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13442,49 +13402,45 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B283" s="4" t="inlineStr">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D283" s="4" t="inlineStr">
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E283" s="4" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F283" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G283" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H283" s="4" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I283" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14666,49 +14622,45 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B311" s="4" t="inlineStr">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C311" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D311" s="4" t="inlineStr">
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E311" s="4" t="inlineStr">
+      <c r="E311" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F311" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G311" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H311" s="4" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I311" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr"/>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15890,49 +15842,45 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B339" s="4" t="inlineStr">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C339" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D339" s="4" t="inlineStr">
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E339" s="4" t="inlineStr">
+      <c r="E339" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F339" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G339" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H339" s="4" t="inlineStr">
-        <is>
-          <t>26/29</t>
-        </is>
-      </c>
-      <c r="I339" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr"/>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -17114,49 +17062,45 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B367" s="4" t="inlineStr">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C367" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D367" s="4" t="inlineStr">
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E367" s="4" t="inlineStr">
+      <c r="E367" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F367" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G367" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H367" s="4" t="inlineStr">
-        <is>
-          <t>26/29</t>
-        </is>
-      </c>
-      <c r="I367" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr"/>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -18338,49 +18282,45 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B395" s="4" t="inlineStr">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C395" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D395" s="4" t="inlineStr">
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E395" s="4" t="inlineStr">
+      <c r="E395" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F395" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G395" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H395" s="4" t="inlineStr">
-        <is>
-          <t>31/33</t>
-        </is>
-      </c>
-      <c r="I395" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr"/>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -19562,49 +19502,45 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B423" s="4" t="inlineStr">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C423" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D423" s="4" t="inlineStr">
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E423" s="4" t="inlineStr">
+      <c r="E423" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F423" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G423" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H423" s="4" t="inlineStr">
-        <is>
-          <t>31/33</t>
-        </is>
-      </c>
-      <c r="I423" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr"/>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -20786,49 +20722,45 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B451" s="4" t="inlineStr">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C451" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D451" s="4" t="inlineStr">
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E451" s="4" t="inlineStr">
+      <c r="E451" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F451" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G451" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H451" s="4" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I451" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr"/>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -22010,49 +21942,45 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B479" s="4" t="inlineStr">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C479" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D479" s="4" t="inlineStr">
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E479" s="4" t="inlineStr">
+      <c r="E479" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F479" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G479" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H479" s="4" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I479" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr"/>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -23234,49 +23162,45 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B507" s="4" t="inlineStr">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C507" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D507" s="4" t="inlineStr">
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E507" s="4" t="inlineStr">
+      <c r="E507" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F507" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G507" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H507" s="4" t="inlineStr">
-        <is>
-          <t>12/27</t>
-        </is>
-      </c>
-      <c r="I507" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr"/>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -24458,49 +24382,45 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B535" s="4" t="inlineStr">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C535" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D535" s="4" t="inlineStr">
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E535" s="4" t="inlineStr">
+      <c r="E535" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F535" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G535" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H535" s="4" t="inlineStr">
-        <is>
-          <t>12/27</t>
-        </is>
-      </c>
-      <c r="I535" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr"/>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -25682,49 +25602,45 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B563" s="4" t="inlineStr">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C563" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D563" s="4" t="inlineStr">
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E563" s="4" t="inlineStr">
+      <c r="E563" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F563" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G563" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H563" s="4" t="inlineStr">
-        <is>
-          <t>17/29</t>
-        </is>
-      </c>
-      <c r="I563" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr"/>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -26906,49 +26822,45 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B591" s="4" t="inlineStr">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C591" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D591" s="4" t="inlineStr">
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E591" s="4" t="inlineStr">
+      <c r="E591" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F591" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G591" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H591" s="4" t="inlineStr">
-        <is>
-          <t>17/29</t>
-        </is>
-      </c>
-      <c r="I591" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G591" s="2" t="inlineStr"/>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I591" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -28130,49 +28042,45 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B619" s="4" t="inlineStr">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C619" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D619" s="4" t="inlineStr">
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E619" s="4" t="inlineStr">
+      <c r="E619" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F619" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G619" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H619" s="4" t="inlineStr">
-        <is>
-          <t>12/29</t>
-        </is>
-      </c>
-      <c r="I619" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr"/>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I619" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -29354,49 +29262,45 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B647" s="4" t="inlineStr">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C647" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D647" s="4" t="inlineStr">
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E647" s="4" t="inlineStr">
+      <c r="E647" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F647" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G647" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H647" s="4" t="inlineStr">
-        <is>
-          <t>12/29</t>
-        </is>
-      </c>
-      <c r="I647" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G647" s="2" t="inlineStr"/>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I647" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -90,10 +90,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -642,112 +642,108 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Total Students</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>B1-1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>21/27</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>19/27</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Total Students</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>B1-1</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Total Sessions</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="4" t="n">
         <v>672</v>
       </c>
     </row>
@@ -793,13 +789,13 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Recorded Sessions</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n">
-        <v>98</v>
+      <c r="L6" s="4" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -844,124 +840,124 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Missing Sessions</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
-        <v>574</v>
+      <c r="L7" s="4" t="n">
+        <v>598</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>18/27</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Pending Sessions</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>24/27</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Coverage %</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>14.6%</t>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -1007,14 +1003,14 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Average Attendance %</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>66.3%</t>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -1282,39 +1278,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="M15" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="N15" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O15" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q15" s="5" t="n">
+      <c r="O15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="inlineStr">
-        <is>
-          <t>75.9%</t>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -1360,39 +1356,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="M16" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="N16" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O16" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q16" s="5" t="n">
+      <c r="O16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>50.8%</t>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>49.5%</t>
         </is>
       </c>
     </row>
@@ -1438,39 +1434,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="M17" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="N17" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O17" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q17" s="5" t="n">
+      <c r="O17" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>33.7%</t>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>38.2%</t>
         </is>
       </c>
     </row>
@@ -1516,39 +1512,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="M18" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="N18" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O18" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q18" s="5" t="n">
+      <c r="O18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>71.4%</t>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -1594,39 +1590,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="M19" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="N19" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O19" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q19" s="5" t="n">
+      <c r="O19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>89.5%</t>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>89.2%</t>
         </is>
       </c>
     </row>
@@ -1672,39 +1668,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="M20" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="N20" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O20" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q20" s="5" t="n">
+      <c r="O20" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>85.7%</t>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>86.9%</t>
         </is>
       </c>
     </row>
@@ -1750,39 +1746,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="M21" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="N21" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O21" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q21" s="5" t="n">
+      <c r="O21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>82.8%</t>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -1828,39 +1824,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="M22" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="N22" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O22" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q22" s="5" t="n">
+      <c r="O22" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>85.6%</t>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -1906,39 +1902,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="M23" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="N23" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O23" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q23" s="5" t="n">
+      <c r="O23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -1984,39 +1980,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="M24" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="N24" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O24" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q24" s="5" t="n">
+      <c r="O24" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>43.5%</t>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>38.3%</t>
         </is>
       </c>
     </row>
@@ -2062,39 +2058,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="M25" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="N25" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O25" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q25" s="5" t="n">
+      <c r="O25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>64.7%</t>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2140,39 +2136,39 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="M26" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="N26" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="O26" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q26" s="5" t="n">
+      <c r="O26" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>53.4%</t>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2406,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -2420,121 +2416,117 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>Session recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Session missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>B1-1</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>21/27</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>19/27</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Session missed</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>B1-1</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2544,7 +2536,7 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>Future session</t>
         </is>
@@ -2637,94 +2629,94 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>18/27</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>24/27</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -3677,94 +3669,90 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>B1-10</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>17/31</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>B1-10</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>15/31</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -3857,94 +3845,94 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>18/31</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>13/31</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -4897,94 +4885,90 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>B1-10</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>17/31</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>B1-10</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>15/31</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -5077,94 +5061,94 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="H92" s="5" t="inlineStr">
         <is>
           <t>18/31</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr">
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <t>13/31</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -6117,94 +6101,90 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>B1-11</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>3/19</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>B1-11</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
+      <c r="H117" s="5" t="inlineStr">
         <is>
           <t>7/19</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr">
+      <c r="I117" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -6297,94 +6277,94 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="E120" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="H120" s="5" t="inlineStr">
         <is>
           <t>11/19</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr">
+      <c r="I120" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="E121" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H121" s="4" t="inlineStr">
+      <c r="H121" s="5" t="inlineStr">
         <is>
           <t>10/19</t>
         </is>
       </c>
-      <c r="I121" s="4" t="inlineStr">
+      <c r="I121" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -6606,47 +6586,47 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H127" s="4" t="inlineStr">
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>1/19</t>
         </is>
       </c>
-      <c r="I127" s="4" t="inlineStr">
+      <c r="I127" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -7341,94 +7321,90 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>B1-11</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>3/19</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>B1-11</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
+      <c r="H145" s="5" t="inlineStr">
         <is>
           <t>7/19</t>
         </is>
       </c>
-      <c r="I145" s="4" t="inlineStr">
+      <c r="I145" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -7521,94 +7497,94 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
+      <c r="E148" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G148" s="4" t="inlineStr">
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr">
+      <c r="H148" s="5" t="inlineStr">
         <is>
           <t>11/19</t>
         </is>
       </c>
-      <c r="I148" s="4" t="inlineStr">
+      <c r="I148" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr">
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H149" s="4" t="inlineStr">
+      <c r="H149" s="5" t="inlineStr">
         <is>
           <t>10/19</t>
         </is>
       </c>
-      <c r="I149" s="4" t="inlineStr">
+      <c r="I149" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -7830,47 +7806,47 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
+      <c r="E155" s="5" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H155" s="4" t="inlineStr">
+      <c r="H155" s="5" t="inlineStr">
         <is>
           <t>1/19</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr">
+      <c r="I155" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -8565,94 +8541,90 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>B1-12</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H172" s="4" t="inlineStr">
+      <c r="H173" s="5" t="inlineStr">
         <is>
           <t>14/21</t>
         </is>
       </c>
-      <c r="I172" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>B1-12</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>14/21</t>
-        </is>
-      </c>
-      <c r="I173" s="4" t="inlineStr">
+      <c r="I173" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -8745,94 +8717,94 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="E176" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr">
+      <c r="H176" s="5" t="inlineStr">
         <is>
           <t>13/21</t>
         </is>
       </c>
-      <c r="I176" s="4" t="inlineStr">
+      <c r="I176" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
+      <c r="E177" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H177" s="4" t="inlineStr">
+      <c r="H177" s="5" t="inlineStr">
         <is>
           <t>19/21</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr">
+      <c r="I177" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -9785,94 +9757,90 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E200" s="4" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F200" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>B1-12</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H200" s="4" t="inlineStr">
+      <c r="H201" s="5" t="inlineStr">
         <is>
           <t>14/21</t>
         </is>
       </c>
-      <c r="I200" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>B1-12</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H201" s="4" t="inlineStr">
-        <is>
-          <t>14/21</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="inlineStr">
+      <c r="I201" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -9965,94 +9933,94 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr">
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E204" s="4" t="inlineStr">
+      <c r="E204" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F204" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G204" s="4" t="inlineStr">
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H204" s="4" t="inlineStr">
+      <c r="H204" s="5" t="inlineStr">
         <is>
           <t>13/21</t>
         </is>
       </c>
-      <c r="I204" s="4" t="inlineStr">
+      <c r="I204" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E205" s="4" t="inlineStr">
+      <c r="E205" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr">
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H205" s="4" t="inlineStr">
+      <c r="H205" s="5" t="inlineStr">
         <is>
           <t>19/21</t>
         </is>
       </c>
-      <c r="I205" s="4" t="inlineStr">
+      <c r="I205" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -11005,94 +10973,90 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D228" s="4" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E228" s="4" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F228" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G228" s="4" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>B1-2</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H228" s="4" t="inlineStr">
+      <c r="H229" s="5" t="inlineStr">
         <is>
           <t>28/31</t>
         </is>
       </c>
-      <c r="I228" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>B1-2</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F229" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G229" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H229" s="4" t="inlineStr">
-        <is>
-          <t>28/31</t>
-        </is>
-      </c>
-      <c r="I229" s="4" t="inlineStr">
+      <c r="I229" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -11185,94 +11149,94 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E232" s="4" t="inlineStr">
+      <c r="E232" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F232" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G232" s="4" t="inlineStr">
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H232" s="4" t="inlineStr">
+      <c r="H232" s="5" t="inlineStr">
         <is>
           <t>24/31</t>
         </is>
       </c>
-      <c r="I232" s="4" t="inlineStr">
+      <c r="I232" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E233" s="4" t="inlineStr">
+      <c r="E233" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F233" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="4" t="inlineStr">
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H233" s="4" t="inlineStr">
+      <c r="H233" s="5" t="inlineStr">
         <is>
           <t>31/31</t>
         </is>
       </c>
-      <c r="I233" s="4" t="inlineStr">
+      <c r="I233" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -12225,94 +12189,90 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D256" s="4" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E256" s="4" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F256" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G256" s="4" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>B1-2</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H256" s="4" t="inlineStr">
+      <c r="H257" s="5" t="inlineStr">
         <is>
           <t>28/31</t>
         </is>
       </c>
-      <c r="I256" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>B1-2</t>
-        </is>
-      </c>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D257" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E257" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F257" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H257" s="4" t="inlineStr">
-        <is>
-          <t>28/31</t>
-        </is>
-      </c>
-      <c r="I257" s="4" t="inlineStr">
+      <c r="I257" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -12405,94 +12365,94 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B260" s="4" t="inlineStr">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C260" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D260" s="4" t="inlineStr">
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E260" s="4" t="inlineStr">
+      <c r="E260" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F260" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G260" s="4" t="inlineStr">
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G260" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H260" s="4" t="inlineStr">
+      <c r="H260" s="5" t="inlineStr">
         <is>
           <t>24/31</t>
         </is>
       </c>
-      <c r="I260" s="4" t="inlineStr">
+      <c r="I260" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B261" s="4" t="inlineStr">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C261" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D261" s="4" t="inlineStr">
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E261" s="4" t="inlineStr">
+      <c r="E261" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F261" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G261" s="4" t="inlineStr">
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H261" s="4" t="inlineStr">
+      <c r="H261" s="5" t="inlineStr">
         <is>
           <t>31/31</t>
         </is>
       </c>
-      <c r="I261" s="4" t="inlineStr">
+      <c r="I261" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -13445,94 +13405,90 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B284" s="4" t="inlineStr">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C284" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D284" s="4" t="inlineStr">
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E284" s="4" t="inlineStr">
+      <c r="E284" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F284" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G284" s="4" t="inlineStr">
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>B1-3</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H284" s="4" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I284" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B285" s="4" t="inlineStr">
-        <is>
-          <t>B1-3</t>
-        </is>
-      </c>
-      <c r="C285" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D285" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E285" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F285" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G285" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H285" s="4" t="inlineStr">
+      <c r="H285" s="5" t="inlineStr">
         <is>
           <t>27/28</t>
         </is>
       </c>
-      <c r="I285" s="4" t="inlineStr">
+      <c r="I285" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -13625,94 +13581,94 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C288" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D288" s="4" t="inlineStr">
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E288" s="4" t="inlineStr">
+      <c r="E288" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F288" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="4" t="inlineStr">
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H288" s="4" t="inlineStr">
+      <c r="H288" s="5" t="inlineStr">
         <is>
           <t>20/28</t>
         </is>
       </c>
-      <c r="I288" s="4" t="inlineStr">
+      <c r="I288" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B289" s="4" t="inlineStr">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C289" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D289" s="4" t="inlineStr">
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E289" s="4" t="inlineStr">
+      <c r="E289" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F289" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G289" s="4" t="inlineStr">
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H289" s="4" t="inlineStr">
+      <c r="H289" s="5" t="inlineStr">
         <is>
           <t>26/28</t>
         </is>
       </c>
-      <c r="I289" s="4" t="inlineStr">
+      <c r="I289" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -14665,94 +14621,90 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B312" s="4" t="inlineStr">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C312" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D312" s="4" t="inlineStr">
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E312" s="4" t="inlineStr">
+      <c r="E312" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F312" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G312" s="4" t="inlineStr">
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr"/>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>B1-3</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G313" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H312" s="4" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I312" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B313" s="4" t="inlineStr">
-        <is>
-          <t>B1-3</t>
-        </is>
-      </c>
-      <c r="C313" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D313" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E313" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F313" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G313" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H313" s="4" t="inlineStr">
+      <c r="H313" s="5" t="inlineStr">
         <is>
           <t>27/28</t>
         </is>
       </c>
-      <c r="I313" s="4" t="inlineStr">
+      <c r="I313" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -14845,94 +14797,94 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B316" s="4" t="inlineStr">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C316" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D316" s="4" t="inlineStr">
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E316" s="4" t="inlineStr">
+      <c r="E316" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F316" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G316" s="4" t="inlineStr">
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H316" s="4" t="inlineStr">
+      <c r="H316" s="5" t="inlineStr">
         <is>
           <t>20/28</t>
         </is>
       </c>
-      <c r="I316" s="4" t="inlineStr">
+      <c r="I316" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B317" s="4" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C317" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D317" s="4" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E317" s="4" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F317" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G317" s="4" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H317" s="4" t="inlineStr">
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>26/28</t>
         </is>
       </c>
-      <c r="I317" s="4" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -15885,94 +15837,90 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B340" s="4" t="inlineStr">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C340" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D340" s="4" t="inlineStr">
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E340" s="4" t="inlineStr">
+      <c r="E340" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F340" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G340" s="4" t="inlineStr">
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr"/>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B341" s="5" t="inlineStr">
+        <is>
+          <t>B1-4</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D341" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F341" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G341" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H340" s="4" t="inlineStr">
-        <is>
-          <t>27/29</t>
-        </is>
-      </c>
-      <c r="I340" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B341" s="4" t="inlineStr">
-        <is>
-          <t>B1-4</t>
-        </is>
-      </c>
-      <c r="C341" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D341" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E341" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F341" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G341" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H341" s="4" t="inlineStr">
+      <c r="H341" s="5" t="inlineStr">
         <is>
           <t>24/29</t>
         </is>
       </c>
-      <c r="I341" s="4" t="inlineStr">
+      <c r="I341" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -16065,94 +16013,94 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B344" s="4" t="inlineStr">
+      <c r="A344" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B344" s="5" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C344" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D344" s="4" t="inlineStr">
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D344" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E344" s="4" t="inlineStr">
+      <c r="E344" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F344" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G344" s="4" t="inlineStr">
+      <c r="F344" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G344" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H344" s="4" t="inlineStr">
+      <c r="H344" s="5" t="inlineStr">
         <is>
           <t>23/29</t>
         </is>
       </c>
-      <c r="I344" s="4" t="inlineStr">
+      <c r="I344" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B345" s="4" t="inlineStr">
+      <c r="A345" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B345" s="5" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C345" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D345" s="4" t="inlineStr">
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D345" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E345" s="4" t="inlineStr">
+      <c r="E345" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F345" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G345" s="4" t="inlineStr">
+      <c r="F345" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G345" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H345" s="4" t="inlineStr">
+      <c r="H345" s="5" t="inlineStr">
         <is>
           <t>22/29</t>
         </is>
       </c>
-      <c r="I345" s="4" t="inlineStr">
+      <c r="I345" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -17105,94 +17053,90 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B368" s="4" t="inlineStr">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C368" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D368" s="4" t="inlineStr">
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E368" s="4" t="inlineStr">
+      <c r="E368" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F368" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G368" s="4" t="inlineStr">
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr"/>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B369" s="5" t="inlineStr">
+        <is>
+          <t>B1-4</t>
+        </is>
+      </c>
+      <c r="C369" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D369" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F369" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G369" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H368" s="4" t="inlineStr">
-        <is>
-          <t>27/29</t>
-        </is>
-      </c>
-      <c r="I368" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B369" s="4" t="inlineStr">
-        <is>
-          <t>B1-4</t>
-        </is>
-      </c>
-      <c r="C369" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D369" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E369" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F369" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G369" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H369" s="4" t="inlineStr">
+      <c r="H369" s="5" t="inlineStr">
         <is>
           <t>24/29</t>
         </is>
       </c>
-      <c r="I369" s="4" t="inlineStr">
+      <c r="I369" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -17285,94 +17229,94 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B372" s="4" t="inlineStr">
+      <c r="A372" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B372" s="5" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C372" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D372" s="4" t="inlineStr">
+      <c r="C372" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D372" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E372" s="4" t="inlineStr">
+      <c r="E372" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F372" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G372" s="4" t="inlineStr">
+      <c r="F372" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G372" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H372" s="4" t="inlineStr">
+      <c r="H372" s="5" t="inlineStr">
         <is>
           <t>23/29</t>
         </is>
       </c>
-      <c r="I372" s="4" t="inlineStr">
+      <c r="I372" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B373" s="4" t="inlineStr">
+      <c r="A373" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C373" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D373" s="4" t="inlineStr">
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D373" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E373" s="4" t="inlineStr">
+      <c r="E373" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F373" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G373" s="4" t="inlineStr">
+      <c r="F373" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G373" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H373" s="4" t="inlineStr">
+      <c r="H373" s="5" t="inlineStr">
         <is>
           <t>22/29</t>
         </is>
       </c>
-      <c r="I373" s="4" t="inlineStr">
+      <c r="I373" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -18325,94 +18269,90 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B396" s="4" t="inlineStr">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C396" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D396" s="4" t="inlineStr">
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E396" s="4" t="inlineStr">
+      <c r="E396" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F396" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G396" s="4" t="inlineStr">
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr"/>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B397" s="5" t="inlineStr">
+        <is>
+          <t>B1-5</t>
+        </is>
+      </c>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D397" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E397" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F397" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G397" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H396" s="4" t="inlineStr">
-        <is>
-          <t>30/33</t>
-        </is>
-      </c>
-      <c r="I396" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B397" s="4" t="inlineStr">
-        <is>
-          <t>B1-5</t>
-        </is>
-      </c>
-      <c r="C397" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D397" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E397" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F397" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G397" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H397" s="4" t="inlineStr">
+      <c r="H397" s="5" t="inlineStr">
         <is>
           <t>28/33</t>
         </is>
       </c>
-      <c r="I397" s="4" t="inlineStr">
+      <c r="I397" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -18505,94 +18445,94 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B400" s="4" t="inlineStr">
+      <c r="A400" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B400" s="5" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C400" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D400" s="4" t="inlineStr">
+      <c r="C400" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D400" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E400" s="4" t="inlineStr">
+      <c r="E400" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F400" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G400" s="4" t="inlineStr">
+      <c r="F400" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G400" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H400" s="4" t="inlineStr">
+      <c r="H400" s="5" t="inlineStr">
         <is>
           <t>25/33</t>
         </is>
       </c>
-      <c r="I400" s="4" t="inlineStr">
+      <c r="I400" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B401" s="4" t="inlineStr">
+      <c r="A401" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C401" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D401" s="4" t="inlineStr">
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D401" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E401" s="4" t="inlineStr">
+      <c r="E401" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F401" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G401" s="4" t="inlineStr">
+      <c r="F401" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G401" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H401" s="4" t="inlineStr">
+      <c r="H401" s="5" t="inlineStr">
         <is>
           <t>30/33</t>
         </is>
       </c>
-      <c r="I401" s="4" t="inlineStr">
+      <c r="I401" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -19545,94 +19485,90 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B424" s="4" t="inlineStr">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C424" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D424" s="4" t="inlineStr">
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E424" s="4" t="inlineStr">
+      <c r="E424" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F424" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G424" s="4" t="inlineStr">
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr"/>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="inlineStr">
+        <is>
+          <t>B1-5</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D425" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E425" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F425" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G425" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H424" s="4" t="inlineStr">
-        <is>
-          <t>30/33</t>
-        </is>
-      </c>
-      <c r="I424" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B425" s="4" t="inlineStr">
-        <is>
-          <t>B1-5</t>
-        </is>
-      </c>
-      <c r="C425" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D425" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E425" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F425" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G425" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H425" s="4" t="inlineStr">
+      <c r="H425" s="5" t="inlineStr">
         <is>
           <t>28/33</t>
         </is>
       </c>
-      <c r="I425" s="4" t="inlineStr">
+      <c r="I425" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -19725,94 +19661,94 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B428" s="4" t="inlineStr">
+      <c r="A428" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B428" s="5" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C428" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D428" s="4" t="inlineStr">
+      <c r="C428" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D428" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E428" s="4" t="inlineStr">
+      <c r="E428" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F428" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G428" s="4" t="inlineStr">
+      <c r="F428" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G428" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H428" s="4" t="inlineStr">
+      <c r="H428" s="5" t="inlineStr">
         <is>
           <t>25/33</t>
         </is>
       </c>
-      <c r="I428" s="4" t="inlineStr">
+      <c r="I428" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B429" s="4" t="inlineStr">
+      <c r="A429" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C429" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D429" s="4" t="inlineStr">
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D429" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E429" s="4" t="inlineStr">
+      <c r="E429" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F429" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G429" s="4" t="inlineStr">
+      <c r="F429" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G429" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H429" s="4" t="inlineStr">
+      <c r="H429" s="5" t="inlineStr">
         <is>
           <t>30/33</t>
         </is>
       </c>
-      <c r="I429" s="4" t="inlineStr">
+      <c r="I429" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -20765,94 +20701,90 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B452" s="4" t="inlineStr">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C452" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D452" s="4" t="inlineStr">
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E452" s="4" t="inlineStr">
+      <c r="E452" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F452" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G452" s="4" t="inlineStr">
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr"/>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="inlineStr">
+        <is>
+          <t>B1-6</t>
+        </is>
+      </c>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D453" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E453" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F453" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G453" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H452" s="4" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I452" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B453" s="4" t="inlineStr">
-        <is>
-          <t>B1-6</t>
-        </is>
-      </c>
-      <c r="C453" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D453" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E453" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F453" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G453" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H453" s="4" t="inlineStr">
+      <c r="H453" s="5" t="inlineStr">
         <is>
           <t>18/30</t>
         </is>
       </c>
-      <c r="I453" s="4" t="inlineStr">
+      <c r="I453" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -20945,94 +20877,94 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B456" s="4" t="inlineStr">
+      <c r="A456" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B456" s="5" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C456" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D456" s="4" t="inlineStr">
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D456" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E456" s="4" t="inlineStr">
+      <c r="E456" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F456" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G456" s="4" t="inlineStr">
+      <c r="F456" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G456" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H456" s="4" t="inlineStr">
+      <c r="H456" s="5" t="inlineStr">
         <is>
           <t>18/30</t>
         </is>
       </c>
-      <c r="I456" s="4" t="inlineStr">
+      <c r="I456" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B457" s="4" t="inlineStr">
+      <c r="A457" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C457" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D457" s="4" t="inlineStr">
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D457" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E457" s="4" t="inlineStr">
+      <c r="E457" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F457" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G457" s="4" t="inlineStr">
+      <c r="F457" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G457" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H457" s="4" t="inlineStr">
+      <c r="H457" s="5" t="inlineStr">
         <is>
           <t>22/30</t>
         </is>
       </c>
-      <c r="I457" s="4" t="inlineStr">
+      <c r="I457" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -21985,94 +21917,90 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B480" s="4" t="inlineStr">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C480" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D480" s="4" t="inlineStr">
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E480" s="4" t="inlineStr">
+      <c r="E480" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F480" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G480" s="4" t="inlineStr">
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr"/>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="inlineStr">
+        <is>
+          <t>B1-6</t>
+        </is>
+      </c>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E481" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G481" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H480" s="4" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I480" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B481" s="4" t="inlineStr">
-        <is>
-          <t>B1-6</t>
-        </is>
-      </c>
-      <c r="C481" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D481" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E481" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F481" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G481" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H481" s="4" t="inlineStr">
+      <c r="H481" s="5" t="inlineStr">
         <is>
           <t>18/30</t>
         </is>
       </c>
-      <c r="I481" s="4" t="inlineStr">
+      <c r="I481" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -22165,94 +22093,94 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B484" s="4" t="inlineStr">
+      <c r="A484" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B484" s="5" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C484" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D484" s="4" t="inlineStr">
+      <c r="C484" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D484" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E484" s="4" t="inlineStr">
+      <c r="E484" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F484" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G484" s="4" t="inlineStr">
+      <c r="F484" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G484" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H484" s="4" t="inlineStr">
+      <c r="H484" s="5" t="inlineStr">
         <is>
           <t>18/30</t>
         </is>
       </c>
-      <c r="I484" s="4" t="inlineStr">
+      <c r="I484" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B485" s="4" t="inlineStr">
+      <c r="A485" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C485" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D485" s="4" t="inlineStr">
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D485" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E485" s="4" t="inlineStr">
+      <c r="E485" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F485" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G485" s="4" t="inlineStr">
+      <c r="F485" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G485" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H485" s="4" t="inlineStr">
+      <c r="H485" s="5" t="inlineStr">
         <is>
           <t>22/30</t>
         </is>
       </c>
-      <c r="I485" s="4" t="inlineStr">
+      <c r="I485" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -23205,94 +23133,90 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B508" s="4" t="inlineStr">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C508" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D508" s="4" t="inlineStr">
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E508" s="4" t="inlineStr">
+      <c r="E508" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F508" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G508" s="4" t="inlineStr">
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr"/>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B509" s="5" t="inlineStr">
+        <is>
+          <t>B1-7</t>
+        </is>
+      </c>
+      <c r="C509" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D509" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E509" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G509" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H508" s="4" t="inlineStr">
-        <is>
-          <t>16/27</t>
-        </is>
-      </c>
-      <c r="I508" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B509" s="4" t="inlineStr">
-        <is>
-          <t>B1-7</t>
-        </is>
-      </c>
-      <c r="C509" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D509" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E509" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F509" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G509" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H509" s="4" t="inlineStr">
+      <c r="H509" s="5" t="inlineStr">
         <is>
           <t>5/27</t>
         </is>
       </c>
-      <c r="I509" s="4" t="inlineStr">
+      <c r="I509" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -23385,94 +23309,94 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B512" s="4" t="inlineStr">
+      <c r="A512" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B512" s="5" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C512" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D512" s="4" t="inlineStr">
+      <c r="C512" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D512" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E512" s="4" t="inlineStr">
+      <c r="E512" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F512" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G512" s="4" t="inlineStr">
+      <c r="F512" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G512" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H512" s="4" t="inlineStr">
+      <c r="H512" s="5" t="inlineStr">
         <is>
           <t>13/27</t>
         </is>
       </c>
-      <c r="I512" s="4" t="inlineStr">
+      <c r="I512" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B513" s="4" t="inlineStr">
+      <c r="A513" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B513" s="5" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C513" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D513" s="4" t="inlineStr">
+      <c r="C513" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D513" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E513" s="4" t="inlineStr">
+      <c r="E513" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F513" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G513" s="4" t="inlineStr">
+      <c r="F513" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G513" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H513" s="4" t="inlineStr">
+      <c r="H513" s="5" t="inlineStr">
         <is>
           <t>13/27</t>
         </is>
       </c>
-      <c r="I513" s="4" t="inlineStr">
+      <c r="I513" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -24425,94 +24349,90 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B536" s="4" t="inlineStr">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C536" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D536" s="4" t="inlineStr">
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E536" s="4" t="inlineStr">
+      <c r="E536" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F536" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G536" s="4" t="inlineStr">
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr"/>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B537" s="5" t="inlineStr">
+        <is>
+          <t>B1-7</t>
+        </is>
+      </c>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D537" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E537" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F537" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G537" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H536" s="4" t="inlineStr">
-        <is>
-          <t>16/27</t>
-        </is>
-      </c>
-      <c r="I536" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B537" s="4" t="inlineStr">
-        <is>
-          <t>B1-7</t>
-        </is>
-      </c>
-      <c r="C537" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D537" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E537" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F537" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G537" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H537" s="4" t="inlineStr">
+      <c r="H537" s="5" t="inlineStr">
         <is>
           <t>5/27</t>
         </is>
       </c>
-      <c r="I537" s="4" t="inlineStr">
+      <c r="I537" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -24605,94 +24525,94 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B540" s="4" t="inlineStr">
+      <c r="A540" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B540" s="5" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C540" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D540" s="4" t="inlineStr">
+      <c r="C540" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D540" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E540" s="4" t="inlineStr">
+      <c r="E540" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F540" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G540" s="4" t="inlineStr">
+      <c r="F540" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G540" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H540" s="4" t="inlineStr">
+      <c r="H540" s="5" t="inlineStr">
         <is>
           <t>13/27</t>
         </is>
       </c>
-      <c r="I540" s="4" t="inlineStr">
+      <c r="I540" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B541" s="4" t="inlineStr">
+      <c r="A541" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B541" s="5" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C541" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D541" s="4" t="inlineStr">
+      <c r="C541" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D541" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E541" s="4" t="inlineStr">
+      <c r="E541" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F541" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G541" s="4" t="inlineStr">
+      <c r="F541" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G541" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H541" s="4" t="inlineStr">
+      <c r="H541" s="5" t="inlineStr">
         <is>
           <t>13/27</t>
         </is>
       </c>
-      <c r="I541" s="4" t="inlineStr">
+      <c r="I541" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -25645,94 +25565,90 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B564" s="4" t="inlineStr">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C564" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D564" s="4" t="inlineStr">
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E564" s="4" t="inlineStr">
+      <c r="E564" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F564" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G564" s="4" t="inlineStr">
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr"/>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B565" s="5" t="inlineStr">
+        <is>
+          <t>B1-8</t>
+        </is>
+      </c>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E565" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F565" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G565" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H564" s="4" t="inlineStr">
-        <is>
-          <t>17/29</t>
-        </is>
-      </c>
-      <c r="I564" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B565" s="4" t="inlineStr">
-        <is>
-          <t>B1-8</t>
-        </is>
-      </c>
-      <c r="C565" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D565" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E565" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F565" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G565" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H565" s="4" t="inlineStr">
+      <c r="H565" s="5" t="inlineStr">
         <is>
           <t>15/29</t>
         </is>
       </c>
-      <c r="I565" s="4" t="inlineStr">
+      <c r="I565" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -25825,94 +25741,94 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B568" s="4" t="inlineStr">
+      <c r="A568" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B568" s="5" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C568" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D568" s="4" t="inlineStr">
+      <c r="C568" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D568" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E568" s="4" t="inlineStr">
+      <c r="E568" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F568" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G568" s="4" t="inlineStr">
+      <c r="F568" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G568" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H568" s="4" t="inlineStr">
+      <c r="H568" s="5" t="inlineStr">
         <is>
           <t>24/29</t>
         </is>
       </c>
-      <c r="I568" s="4" t="inlineStr">
+      <c r="I568" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B569" s="4" t="inlineStr">
+      <c r="A569" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B569" s="5" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C569" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D569" s="4" t="inlineStr">
+      <c r="C569" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D569" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E569" s="4" t="inlineStr">
+      <c r="E569" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F569" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G569" s="4" t="inlineStr">
+      <c r="F569" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G569" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H569" s="4" t="inlineStr">
+      <c r="H569" s="5" t="inlineStr">
         <is>
           <t>19/29</t>
         </is>
       </c>
-      <c r="I569" s="4" t="inlineStr">
+      <c r="I569" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -26865,94 +26781,90 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B592" s="4" t="inlineStr">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C592" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D592" s="4" t="inlineStr">
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E592" s="4" t="inlineStr">
+      <c r="E592" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F592" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G592" s="4" t="inlineStr">
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G592" s="2" t="inlineStr"/>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B593" s="5" t="inlineStr">
+        <is>
+          <t>B1-8</t>
+        </is>
+      </c>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D593" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E593" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F593" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G593" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H592" s="4" t="inlineStr">
-        <is>
-          <t>17/29</t>
-        </is>
-      </c>
-      <c r="I592" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B593" s="4" t="inlineStr">
-        <is>
-          <t>B1-8</t>
-        </is>
-      </c>
-      <c r="C593" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D593" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E593" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F593" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G593" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H593" s="4" t="inlineStr">
+      <c r="H593" s="5" t="inlineStr">
         <is>
           <t>15/29</t>
         </is>
       </c>
-      <c r="I593" s="4" t="inlineStr">
+      <c r="I593" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -27045,94 +26957,94 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B596" s="4" t="inlineStr">
+      <c r="A596" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B596" s="5" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C596" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D596" s="4" t="inlineStr">
+      <c r="C596" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D596" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E596" s="4" t="inlineStr">
+      <c r="E596" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F596" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G596" s="4" t="inlineStr">
+      <c r="F596" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G596" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H596" s="4" t="inlineStr">
+      <c r="H596" s="5" t="inlineStr">
         <is>
           <t>24/29</t>
         </is>
       </c>
-      <c r="I596" s="4" t="inlineStr">
+      <c r="I596" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B597" s="4" t="inlineStr">
+      <c r="A597" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B597" s="5" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C597" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D597" s="4" t="inlineStr">
+      <c r="C597" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D597" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E597" s="4" t="inlineStr">
+      <c r="E597" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F597" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G597" s="4" t="inlineStr">
+      <c r="F597" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G597" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H597" s="4" t="inlineStr">
+      <c r="H597" s="5" t="inlineStr">
         <is>
           <t>19/29</t>
         </is>
       </c>
-      <c r="I597" s="4" t="inlineStr">
+      <c r="I597" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -28085,94 +27997,90 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B620" s="4" t="inlineStr">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C620" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D620" s="4" t="inlineStr">
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E620" s="4" t="inlineStr">
+      <c r="E620" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F620" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G620" s="4" t="inlineStr">
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr"/>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I620" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B621" s="5" t="inlineStr">
+        <is>
+          <t>B1-9</t>
+        </is>
+      </c>
+      <c r="C621" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D621" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E621" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F621" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G621" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H620" s="4" t="inlineStr">
-        <is>
-          <t>13/29</t>
-        </is>
-      </c>
-      <c r="I620" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B621" s="4" t="inlineStr">
-        <is>
-          <t>B1-9</t>
-        </is>
-      </c>
-      <c r="C621" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D621" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E621" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F621" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G621" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H621" s="4" t="inlineStr">
+      <c r="H621" s="5" t="inlineStr">
         <is>
           <t>10/29</t>
         </is>
       </c>
-      <c r="I621" s="4" t="inlineStr">
+      <c r="I621" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -28265,94 +28173,94 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B624" s="4" t="inlineStr">
+      <c r="A624" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B624" s="5" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C624" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D624" s="4" t="inlineStr">
+      <c r="C624" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D624" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E624" s="4" t="inlineStr">
+      <c r="E624" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F624" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G624" s="4" t="inlineStr">
+      <c r="F624" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G624" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H624" s="4" t="inlineStr">
+      <c r="H624" s="5" t="inlineStr">
         <is>
           <t>18/29</t>
         </is>
       </c>
-      <c r="I624" s="4" t="inlineStr">
+      <c r="I624" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B625" s="4" t="inlineStr">
+      <c r="A625" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B625" s="5" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C625" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D625" s="4" t="inlineStr">
+      <c r="C625" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D625" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E625" s="4" t="inlineStr">
+      <c r="E625" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F625" s="4" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G625" s="4" t="inlineStr">
+      <c r="F625" s="5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G625" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H625" s="4" t="inlineStr">
+      <c r="H625" s="5" t="inlineStr">
         <is>
           <t>21/29</t>
         </is>
       </c>
-      <c r="I625" s="4" t="inlineStr">
+      <c r="I625" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -29305,94 +29213,90 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B648" s="4" t="inlineStr">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C648" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D648" s="4" t="inlineStr">
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E648" s="4" t="inlineStr">
+      <c r="E648" s="2" t="inlineStr">
         <is>
           <t>09/12/2025</t>
         </is>
       </c>
-      <c r="F648" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G648" s="4" t="inlineStr">
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G648" s="2" t="inlineStr"/>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I648" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B649" s="5" t="inlineStr">
+        <is>
+          <t>B1-9</t>
+        </is>
+      </c>
+      <c r="C649" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D649" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E649" s="5" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F649" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G649" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H648" s="4" t="inlineStr">
-        <is>
-          <t>13/29</t>
-        </is>
-      </c>
-      <c r="I648" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B649" s="4" t="inlineStr">
-        <is>
-          <t>B1-9</t>
-        </is>
-      </c>
-      <c r="C649" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D649" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E649" s="4" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="F649" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G649" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H649" s="4" t="inlineStr">
+      <c r="H649" s="5" t="inlineStr">
         <is>
           <t>10/29</t>
         </is>
       </c>
-      <c r="I649" s="4" t="inlineStr">
+      <c r="I649" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -29485,94 +29389,94 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B652" s="4" t="inlineStr">
+      <c r="A652" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B652" s="5" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C652" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D652" s="4" t="inlineStr">
+      <c r="C652" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D652" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E652" s="4" t="inlineStr">
+      <c r="E652" s="5" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F652" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G652" s="4" t="inlineStr">
+      <c r="F652" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G652" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H652" s="4" t="inlineStr">
+      <c r="H652" s="5" t="inlineStr">
         <is>
           <t>18/29</t>
         </is>
       </c>
-      <c r="I652" s="4" t="inlineStr">
+      <c r="I652" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B653" s="4" t="inlineStr">
+      <c r="A653" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B653" s="5" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C653" s="4" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D653" s="4" t="inlineStr">
+      <c r="C653" s="5" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D653" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E653" s="4" t="inlineStr">
+      <c r="E653" s="5" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F653" s="4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G653" s="4" t="inlineStr">
+      <c r="F653" s="5" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G653" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H653" s="4" t="inlineStr">
+      <c r="H653" s="5" t="inlineStr">
         <is>
           <t>21/29</t>
         </is>
       </c>
-      <c r="I653" s="4" t="inlineStr">
+      <c r="I653" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -693,49 +693,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -795,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -846,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>598</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +953,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1006,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
     </row>
@@ -1295,22 +1291,22 @@
         <v>56</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1369,22 @@
         <v>56</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1451,22 +1447,22 @@
         <v>56</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1525,22 @@
         <v>56</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -1607,22 +1603,22 @@
         <v>56</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>88.7%</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1681,22 @@
         <v>56</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -1763,22 +1759,22 @@
         <v>56</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1837,22 @@
         <v>56</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1919,22 +1915,22 @@
         <v>56</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1997,22 +1993,22 @@
         <v>56</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -2075,22 +2071,22 @@
         <v>56</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -2153,22 +2149,22 @@
         <v>56</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
     </row>
@@ -2481,49 +2477,45 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -3712,49 +3704,45 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>15/31</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4928,49 +4916,45 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>15/31</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6144,49 +6128,45 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr">
-        <is>
-          <t>7/19</t>
-        </is>
-      </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7364,49 +7344,45 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E145" s="5" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>7/19</t>
-        </is>
-      </c>
-      <c r="I145" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8584,49 +8560,45 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E173" s="5" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G173" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="inlineStr">
-        <is>
-          <t>14/21</t>
-        </is>
-      </c>
-      <c r="I173" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9800,49 +9772,45 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C201" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D201" s="5" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E201" s="5" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H201" s="5" t="inlineStr">
-        <is>
-          <t>14/21</t>
-        </is>
-      </c>
-      <c r="I201" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11016,49 +10984,45 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B229" s="5" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C229" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D229" s="5" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E229" s="5" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr">
-        <is>
-          <t>28/31</t>
-        </is>
-      </c>
-      <c r="I229" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12232,49 +12196,45 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B257" s="5" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C257" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D257" s="5" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E257" s="5" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G257" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H257" s="5" t="inlineStr">
-        <is>
-          <t>28/31</t>
-        </is>
-      </c>
-      <c r="I257" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13448,49 +13408,45 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B285" s="5" t="inlineStr">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C285" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D285" s="5" t="inlineStr">
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E285" s="5" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G285" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H285" s="5" t="inlineStr">
-        <is>
-          <t>27/28</t>
-        </is>
-      </c>
-      <c r="I285" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14664,49 +14620,45 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B313" s="5" t="inlineStr">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C313" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D313" s="5" t="inlineStr">
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E313" s="5" t="inlineStr">
+      <c r="E313" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F313" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G313" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H313" s="5" t="inlineStr">
-        <is>
-          <t>27/28</t>
-        </is>
-      </c>
-      <c r="I313" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr"/>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15880,49 +15832,45 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B341" s="5" t="inlineStr">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C341" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D341" s="5" t="inlineStr">
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E341" s="5" t="inlineStr">
+      <c r="E341" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F341" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G341" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H341" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I341" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr"/>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -17096,49 +17044,45 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B369" s="5" t="inlineStr">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C369" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D369" s="5" t="inlineStr">
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E369" s="5" t="inlineStr">
+      <c r="E369" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F369" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G369" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H369" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I369" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr"/>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -18312,49 +18256,45 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B397" s="5" t="inlineStr">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C397" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D397" s="5" t="inlineStr">
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E397" s="5" t="inlineStr">
+      <c r="E397" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F397" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G397" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H397" s="5" t="inlineStr">
-        <is>
-          <t>28/33</t>
-        </is>
-      </c>
-      <c r="I397" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr"/>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -19528,49 +19468,45 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B425" s="5" t="inlineStr">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C425" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D425" s="5" t="inlineStr">
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E425" s="5" t="inlineStr">
+      <c r="E425" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F425" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G425" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H425" s="5" t="inlineStr">
-        <is>
-          <t>28/33</t>
-        </is>
-      </c>
-      <c r="I425" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr"/>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -20744,49 +20680,45 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B453" s="5" t="inlineStr">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C453" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D453" s="5" t="inlineStr">
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E453" s="5" t="inlineStr">
+      <c r="E453" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F453" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G453" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H453" s="5" t="inlineStr">
-        <is>
-          <t>18/30</t>
-        </is>
-      </c>
-      <c r="I453" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr"/>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -21960,49 +21892,45 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B481" s="5" t="inlineStr">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C481" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D481" s="5" t="inlineStr">
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E481" s="5" t="inlineStr">
+      <c r="E481" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F481" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G481" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H481" s="5" t="inlineStr">
-        <is>
-          <t>18/30</t>
-        </is>
-      </c>
-      <c r="I481" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr"/>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -23176,49 +23104,45 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B509" s="5" t="inlineStr">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C509" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D509" s="5" t="inlineStr">
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E509" s="5" t="inlineStr">
+      <c r="E509" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F509" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G509" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H509" s="5" t="inlineStr">
-        <is>
-          <t>5/27</t>
-        </is>
-      </c>
-      <c r="I509" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr"/>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -24392,49 +24316,45 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B537" s="5" t="inlineStr">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C537" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D537" s="5" t="inlineStr">
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E537" s="5" t="inlineStr">
+      <c r="E537" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F537" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G537" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H537" s="5" t="inlineStr">
-        <is>
-          <t>5/27</t>
-        </is>
-      </c>
-      <c r="I537" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr"/>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -25608,49 +25528,45 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B565" s="5" t="inlineStr">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C565" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D565" s="5" t="inlineStr">
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E565" s="5" t="inlineStr">
+      <c r="E565" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F565" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G565" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H565" s="5" t="inlineStr">
-        <is>
-          <t>15/29</t>
-        </is>
-      </c>
-      <c r="I565" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr"/>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -26824,49 +26740,45 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B593" s="5" t="inlineStr">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C593" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D593" s="5" t="inlineStr">
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E593" s="5" t="inlineStr">
+      <c r="E593" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F593" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G593" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H593" s="5" t="inlineStr">
-        <is>
-          <t>15/29</t>
-        </is>
-      </c>
-      <c r="I593" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr"/>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I593" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -28040,49 +27952,45 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B621" s="5" t="inlineStr">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C621" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D621" s="5" t="inlineStr">
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E621" s="5" t="inlineStr">
+      <c r="E621" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F621" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G621" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H621" s="5" t="inlineStr">
-        <is>
-          <t>10/29</t>
-        </is>
-      </c>
-      <c r="I621" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr"/>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -29256,49 +29164,45 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B649" s="5" t="inlineStr">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C649" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D649" s="5" t="inlineStr">
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E649" s="5" t="inlineStr">
+      <c r="E649" s="2" t="inlineStr">
         <is>
           <t>10/12/2025</t>
         </is>
       </c>
-      <c r="F649" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G649" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H649" s="5" t="inlineStr">
-        <is>
-          <t>10/29</t>
-        </is>
-      </c>
-      <c r="I649" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G649" s="2" t="inlineStr"/>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I649" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -842,53 +842,49 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>622</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>18/27</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -953,7 +949,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1002,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1287,22 @@
         <v>56</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1365,22 @@
         <v>56</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1443,22 @@
         <v>56</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -1525,22 +1521,22 @@
         <v>56</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1599,22 @@
         <v>56</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1681,22 +1677,22 @@
         <v>56</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1755,22 @@
         <v>56</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1837,22 +1833,22 @@
         <v>56</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1911,22 @@
         <v>56</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -1993,17 +1989,17 @@
         <v>56</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -2071,22 +2067,22 @@
         <v>56</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -2149,22 +2145,22 @@
         <v>56</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -2621,49 +2617,45 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>18/27</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3833,49 +3825,45 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>18/31</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5045,49 +5033,45 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>18/31</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6257,49 +6241,45 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>11/19</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7473,49 +7453,45 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E148" s="5" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>11/19</t>
-        </is>
-      </c>
-      <c r="I148" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8689,49 +8665,45 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>13/21</t>
-        </is>
-      </c>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9901,49 +9873,45 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B204" s="5" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D204" s="5" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E204" s="5" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F204" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G204" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H204" s="5" t="inlineStr">
-        <is>
-          <t>13/21</t>
-        </is>
-      </c>
-      <c r="I204" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11113,49 +11081,45 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B232" s="5" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D232" s="5" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E232" s="5" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H232" s="5" t="inlineStr">
-        <is>
-          <t>24/31</t>
-        </is>
-      </c>
-      <c r="I232" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12325,49 +12289,45 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E260" s="5" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H260" s="5" t="inlineStr">
-        <is>
-          <t>24/31</t>
-        </is>
-      </c>
-      <c r="I260" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13537,49 +13497,45 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="inlineStr">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C288" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D288" s="5" t="inlineStr">
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E288" s="5" t="inlineStr">
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F288" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H288" s="5" t="inlineStr">
-        <is>
-          <t>20/28</t>
-        </is>
-      </c>
-      <c r="I288" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14749,49 +14705,45 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B316" s="5" t="inlineStr">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C316" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D316" s="5" t="inlineStr">
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E316" s="5" t="inlineStr">
+      <c r="E316" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G316" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H316" s="5" t="inlineStr">
-        <is>
-          <t>20/28</t>
-        </is>
-      </c>
-      <c r="I316" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr"/>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15961,49 +15913,45 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B344" s="5" t="inlineStr">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C344" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D344" s="5" t="inlineStr">
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E344" s="5" t="inlineStr">
+      <c r="E344" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F344" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G344" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H344" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I344" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr"/>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -17173,49 +17121,45 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B372" s="5" t="inlineStr">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C372" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D372" s="5" t="inlineStr">
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E372" s="5" t="inlineStr">
+      <c r="E372" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F372" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G372" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H372" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I372" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr"/>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -18385,49 +18329,45 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B400" s="5" t="inlineStr">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C400" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D400" s="5" t="inlineStr">
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E400" s="5" t="inlineStr">
+      <c r="E400" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F400" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G400" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H400" s="5" t="inlineStr">
-        <is>
-          <t>25/33</t>
-        </is>
-      </c>
-      <c r="I400" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr"/>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -19597,49 +19537,45 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B428" s="5" t="inlineStr">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C428" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D428" s="5" t="inlineStr">
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E428" s="5" t="inlineStr">
+      <c r="E428" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F428" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G428" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H428" s="5" t="inlineStr">
-        <is>
-          <t>25/33</t>
-        </is>
-      </c>
-      <c r="I428" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr"/>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -20809,49 +20745,45 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B456" s="5" t="inlineStr">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C456" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D456" s="5" t="inlineStr">
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E456" s="5" t="inlineStr">
+      <c r="E456" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F456" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G456" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H456" s="5" t="inlineStr">
-        <is>
-          <t>18/30</t>
-        </is>
-      </c>
-      <c r="I456" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr"/>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -22021,49 +21953,45 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B484" s="5" t="inlineStr">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C484" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D484" s="5" t="inlineStr">
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E484" s="5" t="inlineStr">
+      <c r="E484" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F484" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G484" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H484" s="5" t="inlineStr">
-        <is>
-          <t>18/30</t>
-        </is>
-      </c>
-      <c r="I484" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr"/>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -23233,49 +23161,45 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B512" s="5" t="inlineStr">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C512" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D512" s="5" t="inlineStr">
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E512" s="5" t="inlineStr">
+      <c r="E512" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F512" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G512" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H512" s="5" t="inlineStr">
-        <is>
-          <t>13/27</t>
-        </is>
-      </c>
-      <c r="I512" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr"/>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -24445,49 +24369,45 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B540" s="5" t="inlineStr">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C540" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D540" s="5" t="inlineStr">
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E540" s="5" t="inlineStr">
+      <c r="E540" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F540" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G540" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H540" s="5" t="inlineStr">
-        <is>
-          <t>13/27</t>
-        </is>
-      </c>
-      <c r="I540" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr"/>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -25657,49 +25577,45 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B568" s="5" t="inlineStr">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C568" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D568" s="5" t="inlineStr">
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E568" s="5" t="inlineStr">
+      <c r="E568" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F568" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G568" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H568" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I568" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr"/>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -26869,49 +26785,45 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B596" s="5" t="inlineStr">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C596" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D596" s="5" t="inlineStr">
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E596" s="5" t="inlineStr">
+      <c r="E596" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F596" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G596" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H596" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I596" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr"/>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I596" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -28081,49 +27993,45 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B624" s="5" t="inlineStr">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C624" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D624" s="5" t="inlineStr">
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E624" s="5" t="inlineStr">
+      <c r="E624" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F624" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G624" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H624" s="5" t="inlineStr">
-        <is>
-          <t>18/29</t>
-        </is>
-      </c>
-      <c r="I624" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr"/>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -29293,49 +29201,45 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B652" s="5" t="inlineStr">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C652" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D652" s="5" t="inlineStr">
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E652" s="5" t="inlineStr">
+      <c r="E652" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F652" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G652" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H652" s="5" t="inlineStr">
-        <is>
-          <t>18/29</t>
-        </is>
-      </c>
-      <c r="I652" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G652" s="2" t="inlineStr"/>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I652" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -93,9 +93,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -103,6 +100,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>646</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -897,49 +897,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -949,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
     </row>
@@ -1002,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -1287,22 +1283,22 @@
         <v>56</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1361,22 @@
         <v>56</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1443,22 +1439,22 @@
         <v>56</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -1521,22 +1517,22 @@
         <v>56</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1599,22 +1595,22 @@
         <v>56</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1677,22 +1673,22 @@
         <v>56</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1755,22 +1751,22 @@
         <v>56</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1833,22 +1829,22 @@
         <v>56</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1911,22 +1907,22 @@
         <v>56</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1985,22 @@
         <v>56</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2067,22 +2063,22 @@
         <v>56</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2145,22 +2141,22 @@
         <v>56</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2399,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2461,7 +2457,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2519,7 +2515,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -2660,49 +2656,45 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3868,49 +3860,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>13/31</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5076,49 +5064,45 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>13/31</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6284,49 +6268,45 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>10/19</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6546,47 +6526,47 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E127" s="8" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="H127" s="8" t="inlineStr">
         <is>
           <t>1/19</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I127" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -7496,49 +7476,45 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>10/19</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7758,47 +7734,47 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E155" s="8" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="inlineStr">
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H155" s="5" t="inlineStr">
+      <c r="H155" s="8" t="inlineStr">
         <is>
           <t>1/19</t>
         </is>
       </c>
-      <c r="I155" s="5" t="inlineStr">
+      <c r="I155" s="8" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -8708,49 +8684,45 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E177" s="5" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>19/21</t>
-        </is>
-      </c>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9916,49 +9888,45 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B205" s="5" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C205" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D205" s="5" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E205" s="5" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H205" s="5" t="inlineStr">
-        <is>
-          <t>19/21</t>
-        </is>
-      </c>
-      <c r="I205" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11124,49 +11092,45 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="inlineStr">
-        <is>
-          <t>31/31</t>
-        </is>
-      </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12332,49 +12296,45 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E261" s="5" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H261" s="5" t="inlineStr">
-        <is>
-          <t>31/31</t>
-        </is>
-      </c>
-      <c r="I261" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13540,49 +13500,45 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C289" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D289" s="5" t="inlineStr">
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E289" s="5" t="inlineStr">
+      <c r="E289" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F289" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G289" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H289" s="5" t="inlineStr">
-        <is>
-          <t>26/28</t>
-        </is>
-      </c>
-      <c r="I289" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14748,49 +14704,45 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H317" s="5" t="inlineStr">
-        <is>
-          <t>26/28</t>
-        </is>
-      </c>
-      <c r="I317" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr"/>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15956,49 +15908,45 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B345" s="5" t="inlineStr">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C345" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D345" s="5" t="inlineStr">
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E345" s="5" t="inlineStr">
+      <c r="E345" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F345" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G345" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H345" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I345" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr"/>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -17164,49 +17112,45 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B373" s="5" t="inlineStr">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C373" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D373" s="5" t="inlineStr">
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E373" s="5" t="inlineStr">
+      <c r="E373" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F373" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G373" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H373" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I373" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr"/>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -18372,49 +18316,45 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B401" s="5" t="inlineStr">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C401" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D401" s="5" t="inlineStr">
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E401" s="5" t="inlineStr">
+      <c r="E401" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F401" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G401" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H401" s="5" t="inlineStr">
-        <is>
-          <t>30/33</t>
-        </is>
-      </c>
-      <c r="I401" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr"/>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -19580,49 +19520,45 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B429" s="5" t="inlineStr">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C429" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D429" s="5" t="inlineStr">
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E429" s="5" t="inlineStr">
+      <c r="E429" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F429" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G429" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H429" s="5" t="inlineStr">
-        <is>
-          <t>30/33</t>
-        </is>
-      </c>
-      <c r="I429" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr"/>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -20788,49 +20724,45 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B457" s="5" t="inlineStr">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C457" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D457" s="5" t="inlineStr">
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E457" s="5" t="inlineStr">
+      <c r="E457" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F457" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G457" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H457" s="5" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I457" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr"/>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -21996,49 +21928,45 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B485" s="5" t="inlineStr">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C485" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D485" s="5" t="inlineStr">
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E485" s="5" t="inlineStr">
+      <c r="E485" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F485" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G485" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H485" s="5" t="inlineStr">
-        <is>
-          <t>22/30</t>
-        </is>
-      </c>
-      <c r="I485" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr"/>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -23204,49 +23132,45 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B513" s="5" t="inlineStr">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C513" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D513" s="5" t="inlineStr">
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E513" s="5" t="inlineStr">
+      <c r="E513" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F513" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G513" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H513" s="5" t="inlineStr">
-        <is>
-          <t>13/27</t>
-        </is>
-      </c>
-      <c r="I513" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr"/>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -24412,49 +24336,45 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B541" s="5" t="inlineStr">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C541" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D541" s="5" t="inlineStr">
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E541" s="5" t="inlineStr">
+      <c r="E541" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F541" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G541" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H541" s="5" t="inlineStr">
-        <is>
-          <t>13/27</t>
-        </is>
-      </c>
-      <c r="I541" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr"/>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -25620,49 +25540,45 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B569" s="5" t="inlineStr">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C569" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D569" s="5" t="inlineStr">
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E569" s="5" t="inlineStr">
+      <c r="E569" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F569" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G569" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H569" s="5" t="inlineStr">
-        <is>
-          <t>19/29</t>
-        </is>
-      </c>
-      <c r="I569" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr"/>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -26828,49 +26744,45 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B597" s="5" t="inlineStr">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C597" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D597" s="5" t="inlineStr">
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E597" s="5" t="inlineStr">
+      <c r="E597" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F597" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G597" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H597" s="5" t="inlineStr">
-        <is>
-          <t>19/29</t>
-        </is>
-      </c>
-      <c r="I597" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G597" s="2" t="inlineStr"/>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I597" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -28036,49 +27948,45 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B625" s="5" t="inlineStr">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C625" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D625" s="5" t="inlineStr">
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E625" s="5" t="inlineStr">
+      <c r="E625" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F625" s="5" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G625" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H625" s="5" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I625" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G625" s="2" t="inlineStr"/>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I625" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -29244,49 +29152,45 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B653" s="5" t="inlineStr">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C653" s="5" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D653" s="5" t="inlineStr">
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E653" s="5" t="inlineStr">
+      <c r="E653" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F653" s="5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G653" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H653" s="5" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I653" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F653" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G653" s="2" t="inlineStr"/>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I653" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,9 +100,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -791,7 +788,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +839,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +942,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -998,7 +995,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1439,22 +1436,22 @@
         <v>56</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6526,49 +6523,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E127" s="8" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F127" s="8" t="inlineStr">
-        <is>
-          <t>08:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="inlineStr">
-        <is>
-          <t>1/19</t>
-        </is>
-      </c>
-      <c r="I127" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7734,49 +7727,45 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C155" s="8" t="inlineStr">
-        <is>
-          <t>SURGERY POP QUIZ</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>SURGERY POP QUIZ</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E155" s="8" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F155" s="8" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G155" s="8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H155" s="8" t="inlineStr">
-        <is>
-          <t>1/19</t>
-        </is>
-      </c>
-      <c r="I155" s="8" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>0/19</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
